--- a/FinalModel/input_databases/default/technologies.xlsx
+++ b/FinalModel/input_databases/default/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nzuijder/Documents/MSc_CSP/MfT/Individual_model/Individual/FinalModel/input_databases/default/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3958CF-A302-7048-81ED-84646B21F696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A34584-CA1D-2640-BC49-D90659B4CF97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="static_parameters" sheetId="2" r:id="rId1"/>
@@ -393,10 +393,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -409,6 +406,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -431,11 +440,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2912,2064 +2922,2416 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1">
-        <v>2025</v>
-      </c>
-      <c r="E1">
+      <c r="D1" s="3">
+        <v>2020</v>
+      </c>
+      <c r="E1" s="3">
         <v>2030</v>
       </c>
-      <c r="F1">
+      <c r="F1" s="3">
         <v>2040</v>
       </c>
-      <c r="G1">
+      <c r="G1" s="3">
         <v>2050</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2">
-        <v>1142.1116999999999</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1068.6424999999999</v>
-      </c>
+      <c r="D2" s="3">
+        <v>950</v>
+      </c>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D3">
-        <f>D2*0.05</f>
-        <v>57.105584999999998</v>
-      </c>
-      <c r="G3">
-        <f>G2*0.05</f>
-        <v>53.432124999999999</v>
-      </c>
+      <c r="D3" s="3">
+        <v>47.5</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>0.2</v>
       </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5">
+      <c r="A5" s="4"/>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="3">
         <v>0.6</v>
       </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="3">
         <v>30</v>
       </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="3">
         <v>0.2</v>
       </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D8">
-        <v>4402.5066999999999</v>
-      </c>
-      <c r="G8" s="2">
-        <v>3890.1824000000001</v>
-      </c>
+      <c r="D8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
+      <c r="A9" s="4"/>
+      <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D9">
-        <f>D8*0.05</f>
-        <v>220.12533500000001</v>
-      </c>
-      <c r="G9">
-        <f>G8*0.05</f>
-        <v>194.50912000000002</v>
-      </c>
+      <c r="D9" s="3">
+        <v>125</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
+      <c r="A10" s="4"/>
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D10">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="G10">
-        <f>D10</f>
-        <v>3.0000000000000001E-3</v>
-      </c>
+      <c r="D10" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11">
+      <c r="A11" s="4"/>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="3">
         <v>0.35</v>
       </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
+      <c r="A12" s="4"/>
+      <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="3">
         <v>30</v>
       </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D13">
-        <v>10805.703799999999</v>
-      </c>
-      <c r="G13">
-        <f>D13*0.8</f>
-        <v>8644.5630399999991</v>
+      <c r="D13" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="3">
+        <v>4800</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
+      <c r="A14" s="4"/>
+      <c r="B14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D14">
-        <f>D13*0.05</f>
-        <v>540.28518999999994</v>
-      </c>
-      <c r="G14">
-        <f t="shared" ref="G14:G15" si="0">D14*0.8</f>
-        <v>432.22815199999997</v>
+      <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="3">
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
+      <c r="A15" s="4"/>
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="3">
         <v>0.5</v>
       </c>
-      <c r="G15">
-        <f t="shared" si="0"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="3">
         <v>0.4</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16">
+      <c r="A16" s="4"/>
+      <c r="B16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="3">
         <v>0.4</v>
       </c>
-      <c r="G16">
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="3">
         <v>0.4</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
+      <c r="A17" s="4"/>
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="3">
         <v>40</v>
       </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D18">
-        <v>850.67529999999999</v>
-      </c>
-      <c r="E18">
+      <c r="D18" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E18" s="3">
         <v>760</v>
       </c>
-      <c r="G18">
+      <c r="F18" s="4"/>
+      <c r="G18" s="3">
         <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
+      <c r="A19" s="4"/>
+      <c r="B19" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="3">
         <v>10</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="3">
         <v>8</v>
       </c>
-      <c r="G19">
+      <c r="F19" s="4"/>
+      <c r="G19" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
+      <c r="A20" s="4"/>
+      <c r="B20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="3">
         <v>0.05</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="3">
         <v>0.05</v>
       </c>
-      <c r="G20">
+      <c r="F20" s="4"/>
+      <c r="G20" s="3">
         <v>0.05</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21">
+      <c r="A21" s="4"/>
+      <c r="B21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="3">
         <v>1</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="3">
         <v>1</v>
       </c>
-      <c r="G21">
+      <c r="F21" s="4"/>
+      <c r="G21" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
+      <c r="A22" s="4"/>
+      <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="3">
         <v>25</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="3">
         <v>25</v>
       </c>
-      <c r="G22">
+      <c r="F22" s="4"/>
+      <c r="G22" s="3">
         <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="A23" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D23">
-        <v>1438.8844999999999</v>
-      </c>
-      <c r="E23">
+      <c r="D23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1300</v>
       </c>
-      <c r="G23">
+      <c r="F23" s="4"/>
+      <c r="G23" s="3">
         <v>1000</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
+      <c r="A24" s="4"/>
+      <c r="B24" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="3">
         <v>30</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="3">
         <v>25</v>
       </c>
-      <c r="G24">
+      <c r="F24" s="4"/>
+      <c r="G24" s="3">
         <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
+      <c r="A25" s="4"/>
+      <c r="B25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="3">
         <v>0.1</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="3">
         <v>0.1</v>
       </c>
-      <c r="G25">
+      <c r="F25" s="4"/>
+      <c r="G25" s="3">
         <v>0.1</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26">
+      <c r="A26" s="4"/>
+      <c r="B26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="3">
         <v>1</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="3">
         <v>1</v>
       </c>
-      <c r="G26">
+      <c r="F26" s="4"/>
+      <c r="G26" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
+      <c r="A27" s="4"/>
+      <c r="B27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="3">
         <v>25</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="3">
         <v>25</v>
       </c>
-      <c r="G27">
+      <c r="F27" s="4"/>
+      <c r="G27" s="3">
         <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="A28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D28">
-        <v>2224.3721</v>
-      </c>
-      <c r="E28">
+      <c r="D28" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E28" s="3">
         <v>2000</v>
       </c>
-      <c r="G28">
+      <c r="F28" s="4"/>
+      <c r="G28" s="3">
         <v>1300</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
+      <c r="A29" s="4"/>
+      <c r="B29" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D29">
-        <f>0.05*D28</f>
-        <v>111.21860500000001</v>
-      </c>
-      <c r="E29">
-        <f>0.05*E28</f>
+      <c r="D29" s="3">
+        <v>125</v>
+      </c>
+      <c r="E29" s="3">
         <v>100</v>
       </c>
-      <c r="G29">
-        <f>0.05*G28</f>
+      <c r="F29" s="4"/>
+      <c r="G29" s="3">
         <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
+      <c r="A30" s="4"/>
+      <c r="B30" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="3">
         <v>0.1</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="3">
         <v>0.1</v>
       </c>
-      <c r="G30">
+      <c r="F30" s="4"/>
+      <c r="G30" s="3">
         <v>0.1</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31">
+      <c r="A31" s="4"/>
+      <c r="B31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="3">
         <v>1.2</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="3">
         <v>1.2</v>
       </c>
-      <c r="G31">
+      <c r="F31" s="4"/>
+      <c r="G31" s="3">
         <v>1.2</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
+      <c r="A32" s="4"/>
+      <c r="B32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="3">
         <v>25</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="3">
         <v>25</v>
       </c>
-      <c r="G32">
+      <c r="F32" s="4"/>
+      <c r="G32" s="3">
         <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="A33" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="3">
+        <v>700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>350</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="4"/>
+      <c r="B34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="4"/>
+      <c r="B35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="4"/>
+      <c r="B36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="3">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="4"/>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="3">
+        <v>25</v>
+      </c>
+      <c r="E37" s="3">
+        <v>25</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E38" s="3">
+        <v>28000</v>
+      </c>
+      <c r="F38" s="3">
+        <v>22400</v>
+      </c>
+      <c r="G38" s="3">
+        <v>17920</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="4"/>
+      <c r="B39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="3">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="4"/>
+      <c r="B40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="3">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="4"/>
+      <c r="B41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="F41" s="3">
+        <v>6.12</v>
+      </c>
+      <c r="G41" s="3">
+        <v>6.12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="4"/>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="3">
+        <v>12</v>
+      </c>
+      <c r="E42" s="3">
+        <v>12</v>
+      </c>
+      <c r="F42" s="3">
+        <v>12</v>
+      </c>
+      <c r="G42" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>9600</v>
+      </c>
+      <c r="G43" s="3">
+        <v>7680</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="4"/>
+      <c r="B44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="4"/>
+      <c r="B45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="4"/>
+      <c r="B46" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="F46" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="G46" s="3">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="4"/>
+      <c r="B47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="3">
+        <v>12</v>
+      </c>
+      <c r="E47" s="3">
+        <v>12</v>
+      </c>
+      <c r="F47" s="3">
+        <v>12</v>
+      </c>
+      <c r="G47" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="4"/>
+      <c r="B48" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D48" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" s="3">
+        <v>300</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="4"/>
+      <c r="B50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="3">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="4"/>
+      <c r="B51" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" s="3">
+        <v>0</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="4"/>
+      <c r="B52" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="4"/>
+      <c r="D52" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="3">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="4"/>
+      <c r="B53" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="3">
+        <v>10</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="4"/>
+      <c r="B55" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D55" s="3">
+        <v>125</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="4"/>
+      <c r="B56" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="4"/>
+      <c r="B57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="4"/>
+      <c r="D57" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="4"/>
+      <c r="B58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="3">
+        <v>35</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="4"/>
+      <c r="B59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D59" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="4"/>
+      <c r="B60" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D60" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="3">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="4"/>
+      <c r="B62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="3">
         <v>250</v>
       </c>
-      <c r="E33">
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="4"/>
+      <c r="B63" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D63" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="4"/>
+      <c r="B64" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" s="4"/>
+      <c r="D64" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="4"/>
+      <c r="B65" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="3">
+        <v>30</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="4"/>
+      <c r="B66" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D66" s="3">
+        <v>-0.38</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="3">
+        <v>-396</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" s="4"/>
+      <c r="B67" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D67" s="3">
+        <v>0.38</v>
+      </c>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="3">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D68" s="3">
+        <v>200</v>
+      </c>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" s="4"/>
+      <c r="B69" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" s="3">
+        <v>10</v>
+      </c>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" s="4"/>
+      <c r="B70" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70" s="3">
+        <v>0</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" s="4"/>
+      <c r="B71" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C71" s="4"/>
+      <c r="D71" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="E71" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="4"/>
+      <c r="B72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" s="3">
+        <v>12</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" s="4"/>
+      <c r="B73" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D73" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E74" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" s="4"/>
+      <c r="B75" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" s="3">
+        <v>100</v>
+      </c>
+      <c r="E75" s="3">
+        <v>75</v>
+      </c>
+      <c r="F75" s="4"/>
+      <c r="G75" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" s="4"/>
+      <c r="B76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D76" s="3">
+        <v>0</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" s="4"/>
+      <c r="B77" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C77" s="4"/>
+      <c r="D77" s="3">
+        <v>3</v>
+      </c>
+      <c r="E77" s="3">
+        <v>4</v>
+      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" s="4"/>
+      <c r="B78" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" s="3">
+        <v>12</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D79" s="3">
+        <v>450</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="4"/>
+      <c r="B80" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D80" s="3">
+        <v>22.5</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" s="4"/>
+      <c r="B81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D81" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" s="4"/>
+      <c r="B82" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" s="4"/>
+      <c r="D82" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="3">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" s="4"/>
+      <c r="B83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" s="3">
+        <v>20</v>
+      </c>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" s="4"/>
+      <c r="B84" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D84" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D85" s="3">
+        <v>900</v>
+      </c>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" s="4"/>
+      <c r="B86" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" s="3">
+        <v>45</v>
+      </c>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" s="4"/>
+      <c r="B87" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D87" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" s="4"/>
+      <c r="B88" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" s="4"/>
+      <c r="D88" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="3">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" s="4"/>
+      <c r="B89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89" s="3">
+        <v>20</v>
+      </c>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" s="4"/>
+      <c r="B90" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D90" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A91" s="4"/>
+      <c r="B91" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D91" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="3">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D92" s="3">
         <v>350</v>
       </c>
-      <c r="G33">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" s="4"/>
+      <c r="B93" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C93" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D34">
+      <c r="D93" s="3">
+        <v>17.5</v>
+      </c>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94" s="4"/>
+      <c r="B94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D94" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" s="4"/>
+      <c r="B95" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95" s="4"/>
+      <c r="D95" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="3">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A96" s="4"/>
+      <c r="B96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" s="3">
+        <v>15</v>
+      </c>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97" s="3">
+        <v>900</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" s="4"/>
+      <c r="B98" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D98" s="3">
+        <v>45</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" s="4"/>
+      <c r="B99" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D99" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" s="4"/>
+      <c r="B100" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="4"/>
+      <c r="D100" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="3">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" s="4"/>
+      <c r="B101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" s="3">
+        <v>20</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102" s="4"/>
+      <c r="B102" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D102" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D103" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104" s="4"/>
+      <c r="B104" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D104" s="3">
+        <v>90</v>
+      </c>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" s="4"/>
+      <c r="B105" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D105" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106" s="4"/>
+      <c r="B106" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C106" s="4"/>
+      <c r="D106" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" s="4"/>
+      <c r="B107" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107" s="3">
+        <v>20</v>
+      </c>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" s="4"/>
+      <c r="B108" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D108" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" s="4"/>
+      <c r="B109" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D109" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="3">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D110" s="3">
         <v>0</v>
       </c>
-      <c r="E34">
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111" s="4"/>
+      <c r="B111" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D111" s="3">
         <v>0</v>
       </c>
-      <c r="G34">
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A112" s="4"/>
+      <c r="B112" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D112" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="4"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" s="4"/>
+      <c r="B113" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D113" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="4"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A114" s="4"/>
+      <c r="B114" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" s="3">
+        <v>4</v>
+      </c>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="4"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D115" s="3">
+        <v>0</v>
+      </c>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4"/>
+      <c r="G115" s="4"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A116" s="4"/>
+      <c r="B116" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D116" s="3">
+        <v>0</v>
+      </c>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+      <c r="G116" s="4"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117" s="4"/>
+      <c r="B117" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C117" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D35">
+      <c r="D117" s="3">
         <v>0</v>
       </c>
-      <c r="E35">
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
+      <c r="G117" s="4"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118" s="4"/>
+      <c r="B118" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D118" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4"/>
+      <c r="G118" s="4"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119" s="4"/>
+      <c r="B119" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D119" s="3">
+        <v>4</v>
+      </c>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="4"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" s="4"/>
+      <c r="B120" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D120" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4"/>
+      <c r="G120" s="4"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" s="3">
         <v>0</v>
       </c>
-      <c r="G35">
+      <c r="E121" s="4"/>
+      <c r="F121" s="4"/>
+      <c r="G121" s="4"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A122" s="4"/>
+      <c r="B122" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D122" s="3">
+        <v>48</v>
+      </c>
+      <c r="E122" s="4"/>
+      <c r="F122" s="4"/>
+      <c r="G122" s="4"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A123" s="4"/>
+      <c r="B123" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D123" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E123" s="4"/>
+      <c r="F123" s="4"/>
+      <c r="G123" s="4"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124" s="4"/>
+      <c r="B124" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" s="4"/>
+      <c r="D124" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="E124" s="4"/>
+      <c r="F124" s="4"/>
+      <c r="G124" s="4"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A125" s="4"/>
+      <c r="B125" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" s="3">
+        <v>4</v>
+      </c>
+      <c r="E125" s="4"/>
+      <c r="F125" s="4"/>
+      <c r="G125" s="4"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A126" s="4"/>
+      <c r="B126" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D126" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E126" s="4"/>
+      <c r="F126" s="4"/>
+      <c r="G126" s="4"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A127" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D127" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36">
-        <v>0.95</v>
-      </c>
-      <c r="E36">
-        <v>0.95</v>
-      </c>
-      <c r="G36">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
+      <c r="E127" s="4"/>
+      <c r="F127" s="4"/>
+      <c r="G127" s="4"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128" s="4"/>
+      <c r="B128" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" s="3">
+        <v>0</v>
+      </c>
+      <c r="E128" s="4"/>
+      <c r="F128" s="4"/>
+      <c r="G128" s="4"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="4"/>
+      <c r="B129" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D129" s="3">
+        <v>0</v>
+      </c>
+      <c r="E129" s="4"/>
+      <c r="F129" s="4"/>
+      <c r="G129" s="4"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="4"/>
+      <c r="B130" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C130" s="4"/>
+      <c r="D130" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="E130" s="4"/>
+      <c r="F130" s="4"/>
+      <c r="G130" s="4"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="4"/>
+      <c r="B131" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C131" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D37">
-        <v>25</v>
-      </c>
-      <c r="E37">
-        <v>25</v>
-      </c>
-      <c r="G37">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>18</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="D131" s="3">
+        <v>4</v>
+      </c>
+      <c r="E131" s="4"/>
+      <c r="F131" s="4"/>
+      <c r="G131" s="4"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="4"/>
+      <c r="B132" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D132" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E132" s="4"/>
+      <c r="F132" s="4"/>
+      <c r="G132" s="4"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B133" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D38">
-        <v>35000</v>
-      </c>
-      <c r="E38">
-        <f>D38*0.8</f>
-        <v>28000</v>
-      </c>
-      <c r="F38">
-        <f t="shared" ref="F38:G38" si="1">E38*0.8</f>
-        <v>22400</v>
-      </c>
-      <c r="G38">
-        <f t="shared" si="1"/>
-        <v>17920</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
+      <c r="C133" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D133" s="3">
+        <v>0</v>
+      </c>
+      <c r="E133" s="4"/>
+      <c r="F133" s="4"/>
+      <c r="G133" s="4"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="4"/>
+      <c r="B134" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C39" t="s">
-        <v>23</v>
-      </c>
-      <c r="D39">
+      <c r="C134" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D134" s="3">
+        <v>20</v>
+      </c>
+      <c r="E134" s="4"/>
+      <c r="F134" s="4"/>
+      <c r="G134" s="4"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="4"/>
+      <c r="B135" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D135" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E135" s="4"/>
+      <c r="F135" s="4"/>
+      <c r="G135" s="4"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="4"/>
+      <c r="B136" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136" s="4"/>
+      <c r="D136" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="E136" s="4"/>
+      <c r="F136" s="4"/>
+      <c r="G136" s="4"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="4"/>
+      <c r="B137" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D137" s="3">
+        <v>4</v>
+      </c>
+      <c r="E137" s="4"/>
+      <c r="F137" s="4"/>
+      <c r="G137" s="4"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="4"/>
+      <c r="B138" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D138" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E138" s="4"/>
+      <c r="F138" s="4"/>
+      <c r="G138" s="4"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D139" s="3">
         <v>0</v>
       </c>
-      <c r="E39">
+      <c r="E139" s="4"/>
+      <c r="F139" s="4"/>
+      <c r="G139" s="4"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="4"/>
+      <c r="B140" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D140" s="3">
         <v>0</v>
       </c>
-      <c r="F39">
+      <c r="E140" s="4"/>
+      <c r="F140" s="4"/>
+      <c r="G140" s="4"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="4"/>
+      <c r="B141" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D141" s="3">
         <v>0</v>
       </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" t="s">
-        <v>22</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B41" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41">
-        <v>3.6</v>
-      </c>
-      <c r="E41">
-        <v>5.6</v>
-      </c>
-      <c r="F41">
-        <v>6.12</v>
-      </c>
-      <c r="G41">
-        <v>6.12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
+      <c r="E141" s="4"/>
+      <c r="F141" s="4"/>
+      <c r="G141" s="4"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="4"/>
+      <c r="B142" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="4"/>
+      <c r="D142" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="E142" s="4"/>
+      <c r="F142" s="4"/>
+      <c r="G142" s="4"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="4"/>
+      <c r="B143" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C143" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D42">
-        <v>12</v>
-      </c>
-      <c r="E42">
-        <v>12</v>
-      </c>
-      <c r="F42">
-        <v>12</v>
-      </c>
-      <c r="G42">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>36</v>
-      </c>
-      <c r="B43" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" t="s">
-        <v>23</v>
-      </c>
-      <c r="D43">
-        <v>15000</v>
-      </c>
-      <c r="E43">
-        <f>D43*0.8</f>
-        <v>12000</v>
-      </c>
-      <c r="F43">
-        <f t="shared" ref="F43:G43" si="2">E43*0.8</f>
-        <v>9600</v>
-      </c>
-      <c r="G43">
-        <f t="shared" si="2"/>
-        <v>7680</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B44" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" t="s">
-        <v>23</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" t="s">
-        <v>20</v>
-      </c>
-      <c r="D46">
-        <v>2.16</v>
-      </c>
-      <c r="E46">
-        <v>2.16</v>
-      </c>
-      <c r="F46">
-        <v>2.16</v>
-      </c>
-      <c r="G46">
-        <v>2.16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" t="s">
-        <v>11</v>
-      </c>
-      <c r="D47">
-        <v>12</v>
-      </c>
-      <c r="E47">
-        <v>12</v>
-      </c>
-      <c r="F47">
-        <v>12</v>
-      </c>
-      <c r="G47">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B48" t="s">
+      <c r="D143" s="3">
+        <v>4</v>
+      </c>
+      <c r="E143" s="4"/>
+      <c r="F143" s="4"/>
+      <c r="G143" s="4"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="4"/>
+      <c r="B144" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C144" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D48">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" t="s">
-        <v>21</v>
-      </c>
-      <c r="D49">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B50" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" t="s">
-        <v>21</v>
-      </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B51" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" t="s">
-        <v>22</v>
-      </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B52" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52">
-        <v>0.7</v>
-      </c>
-      <c r="G52">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B53" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" t="s">
-        <v>11</v>
-      </c>
-      <c r="D53">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>64</v>
-      </c>
-      <c r="B54" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" t="s">
-        <v>21</v>
-      </c>
-      <c r="D54">
-        <f>2.6*D2</f>
-        <v>2969.4904200000001</v>
-      </c>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1">
-        <f>G2*2</f>
-        <v>2137.2849999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" t="s">
-        <v>21</v>
-      </c>
-      <c r="D55">
-        <f>D54*0.05</f>
-        <v>148.47452100000001</v>
-      </c>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55">
-        <f>G54*0.05</f>
-        <v>106.86425</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B56" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" t="s">
-        <v>22</v>
-      </c>
-      <c r="D56">
-        <v>0.4</v>
-      </c>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B57" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B58" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" t="s">
-        <v>11</v>
-      </c>
-      <c r="D58">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B59" t="s">
-        <v>44</v>
-      </c>
-      <c r="C59" t="s">
-        <v>45</v>
-      </c>
-      <c r="D59">
-        <f>0.2*0.15</f>
-        <v>0.03</v>
-      </c>
-      <c r="G59">
-        <f>0.2*0.05</f>
-        <v>1.0000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B60" t="s">
-        <v>68</v>
-      </c>
-      <c r="C60" t="s">
-        <v>45</v>
-      </c>
-      <c r="D60">
-        <f>0.2*0.85</f>
-        <v>0.17</v>
-      </c>
-      <c r="G60">
-        <f>0.2*0.95</f>
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>70</v>
-      </c>
-      <c r="B61" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" t="s">
-        <v>21</v>
-      </c>
-      <c r="D61">
-        <f>D8*2</f>
-        <v>8805.0133999999998</v>
-      </c>
-      <c r="G61">
-        <f>G8*2</f>
-        <v>7780.3648000000003</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B62" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" t="s">
-        <v>21</v>
-      </c>
-      <c r="D62">
-        <f>D61*0.05</f>
-        <v>440.25067000000001</v>
-      </c>
-      <c r="G62">
-        <f>G61*0.05</f>
-        <v>389.01824000000005</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B63" t="s">
-        <v>8</v>
-      </c>
-      <c r="C63" t="s">
-        <v>22</v>
-      </c>
-      <c r="D63">
-        <f>0.003*2</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="G63">
-        <f>G10*2</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B64" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B65" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" t="s">
-        <v>11</v>
-      </c>
-      <c r="D65">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B66" t="s">
-        <v>44</v>
-      </c>
-      <c r="C66" t="s">
-        <v>45</v>
-      </c>
-      <c r="D66">
-        <f>-D67</f>
-        <v>-0.38</v>
-      </c>
-      <c r="G66">
-        <f>-G67</f>
-        <v>-0.39600000000000002</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B67" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D67">
-        <f>2*0.2*0.95</f>
-        <v>0.38</v>
-      </c>
-      <c r="G67">
-        <f>2*0.2*0.99</f>
-        <v>0.39600000000000002</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>72</v>
-      </c>
-      <c r="B68" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" t="s">
-        <v>21</v>
-      </c>
-      <c r="D68">
-        <v>200</v>
-      </c>
-      <c r="G68">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B69" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" t="s">
-        <v>21</v>
-      </c>
-      <c r="D69">
-        <f>D68*0.05</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B70" t="s">
-        <v>8</v>
-      </c>
-      <c r="C70" t="s">
-        <v>22</v>
-      </c>
-      <c r="D70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B71" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71">
-        <v>0.9</v>
-      </c>
-      <c r="E71">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B72" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" t="s">
-        <v>11</v>
-      </c>
-      <c r="D72">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B73" t="s">
-        <v>44</v>
-      </c>
-      <c r="C73" t="s">
-        <v>45</v>
-      </c>
-      <c r="D73">
+      <c r="D144" s="3">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>75</v>
-      </c>
-      <c r="B74" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" t="s">
-        <v>21</v>
-      </c>
-      <c r="D74">
-        <v>2000</v>
-      </c>
-      <c r="E74">
-        <v>1500</v>
-      </c>
-      <c r="G74">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B75" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" t="s">
-        <v>21</v>
-      </c>
-      <c r="D75">
-        <f>D74*0.05</f>
-        <v>100</v>
-      </c>
-      <c r="E75">
-        <f>E74*0.05</f>
-        <v>75</v>
-      </c>
-      <c r="G75">
-        <f>G74*0.05</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B76" t="s">
-        <v>8</v>
-      </c>
-      <c r="C76" t="s">
-        <v>22</v>
-      </c>
-      <c r="D76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B77" t="s">
-        <v>9</v>
-      </c>
-      <c r="D77">
-        <v>3</v>
-      </c>
-      <c r="E77">
-        <v>4</v>
-      </c>
-      <c r="G77">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B78" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" t="s">
-        <v>11</v>
-      </c>
-      <c r="D78">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>77</v>
-      </c>
-      <c r="B79" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" t="s">
-        <v>21</v>
-      </c>
-      <c r="D79">
-        <v>450</v>
-      </c>
-      <c r="G79">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B80" t="s">
-        <v>7</v>
-      </c>
-      <c r="C80" t="s">
-        <v>21</v>
-      </c>
-      <c r="D80">
-        <f>D79*0.05</f>
-        <v>22.5</v>
-      </c>
-      <c r="G80">
-        <f>G79*0.05</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B81" t="s">
-        <v>8</v>
-      </c>
-      <c r="C81" t="s">
-        <v>22</v>
-      </c>
-      <c r="D81">
-        <v>0.2</v>
-      </c>
-      <c r="G81">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B82" t="s">
-        <v>9</v>
-      </c>
-      <c r="D82">
-        <v>0.85</v>
-      </c>
-      <c r="G82">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B83" t="s">
-        <v>10</v>
-      </c>
-      <c r="C83" t="s">
-        <v>11</v>
-      </c>
-      <c r="D83">
-        <v>20</v>
-      </c>
-      <c r="G83">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B84" t="s">
-        <v>44</v>
-      </c>
-      <c r="C84" t="s">
-        <v>45</v>
-      </c>
-      <c r="D84">
-        <v>0.2</v>
-      </c>
-      <c r="G84">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>81</v>
-      </c>
-      <c r="B85" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" t="s">
-        <v>21</v>
-      </c>
-      <c r="D85">
-        <f>D79*2</f>
-        <v>900</v>
-      </c>
-      <c r="G85">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B86" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" t="s">
-        <v>21</v>
-      </c>
-      <c r="D86">
-        <f>D85*0.05</f>
-        <v>45</v>
-      </c>
-      <c r="G86">
-        <f>G85*0.05</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B87" t="s">
-        <v>8</v>
-      </c>
-      <c r="C87" t="s">
-        <v>22</v>
-      </c>
-      <c r="D87">
-        <v>0.4</v>
-      </c>
-      <c r="G87">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B88" t="s">
-        <v>9</v>
-      </c>
-      <c r="D88">
-        <v>0.8</v>
-      </c>
-      <c r="G88">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B89" t="s">
-        <v>10</v>
-      </c>
-      <c r="C89" t="s">
-        <v>11</v>
-      </c>
-      <c r="D89">
-        <v>20</v>
-      </c>
-      <c r="G89">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B90" t="s">
-        <v>44</v>
-      </c>
-      <c r="C90" t="s">
-        <v>45</v>
-      </c>
-      <c r="D90">
-        <f>0.2*0.15</f>
-        <v>0.03</v>
-      </c>
-      <c r="G90">
-        <f>0.2*0.1</f>
-        <v>2.0000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B91" t="s">
-        <v>68</v>
-      </c>
-      <c r="C91" t="s">
-        <v>45</v>
-      </c>
-      <c r="D91">
-        <f>0.2*0.85</f>
-        <v>0.17</v>
-      </c>
-      <c r="G91">
-        <f>0.2*0.9</f>
-        <v>0.18000000000000002</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>83</v>
-      </c>
-      <c r="B92" t="s">
-        <v>6</v>
-      </c>
-      <c r="C92" t="s">
-        <v>21</v>
-      </c>
-      <c r="D92">
-        <v>350</v>
-      </c>
-      <c r="G92">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B93" t="s">
-        <v>7</v>
-      </c>
-      <c r="C93" t="s">
-        <v>21</v>
-      </c>
-      <c r="D93">
-        <f>D92*0.05</f>
-        <v>17.5</v>
-      </c>
-      <c r="G93">
-        <f>G92*0.05</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B94" t="s">
-        <v>8</v>
-      </c>
-      <c r="C94" t="s">
-        <v>22</v>
-      </c>
-      <c r="D94">
-        <v>0.2</v>
-      </c>
-      <c r="G94">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B95" t="s">
-        <v>9</v>
-      </c>
-      <c r="D95">
-        <v>0.95</v>
-      </c>
-      <c r="G95">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B96" t="s">
-        <v>10</v>
-      </c>
-      <c r="C96" t="s">
-        <v>11</v>
-      </c>
-      <c r="D96">
-        <v>15</v>
-      </c>
-      <c r="G96">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
-        <v>85</v>
-      </c>
-      <c r="B97" t="s">
-        <v>6</v>
-      </c>
-      <c r="C97" t="s">
-        <v>21</v>
-      </c>
-      <c r="D97">
-        <v>900</v>
-      </c>
-      <c r="G97">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B98" t="s">
-        <v>7</v>
-      </c>
-      <c r="C98" t="s">
-        <v>21</v>
-      </c>
-      <c r="D98">
-        <f>D97*0.05</f>
-        <v>45</v>
-      </c>
-      <c r="G98">
-        <f>G97*0.05</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B99" t="s">
-        <v>8</v>
-      </c>
-      <c r="C99" t="s">
-        <v>22</v>
-      </c>
-      <c r="D99">
-        <v>0.2</v>
-      </c>
-      <c r="G99">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B100" t="s">
-        <v>9</v>
-      </c>
-      <c r="D100">
-        <v>0.6</v>
-      </c>
-      <c r="G100">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B101" t="s">
-        <v>10</v>
-      </c>
-      <c r="C101" t="s">
-        <v>11</v>
-      </c>
-      <c r="D101">
-        <v>20</v>
-      </c>
-      <c r="G101">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B102" t="s">
-        <v>44</v>
-      </c>
-      <c r="C102" t="s">
-        <v>45</v>
-      </c>
-      <c r="D102">
-        <v>0.2</v>
-      </c>
-      <c r="G102">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
-        <v>88</v>
-      </c>
-      <c r="B103" t="s">
-        <v>6</v>
-      </c>
-      <c r="C103" t="s">
-        <v>21</v>
-      </c>
-      <c r="D103">
-        <f>D97*2</f>
-        <v>1800</v>
-      </c>
-      <c r="G103">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B104" t="s">
-        <v>7</v>
-      </c>
-      <c r="C104" t="s">
-        <v>21</v>
-      </c>
-      <c r="D104">
-        <f>D103*0.05</f>
-        <v>90</v>
-      </c>
-      <c r="G104">
-        <f>G103*0.05</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B105" t="s">
-        <v>8</v>
-      </c>
-      <c r="C105" t="s">
-        <v>22</v>
-      </c>
-      <c r="D105">
-        <v>0.4</v>
-      </c>
-      <c r="G105">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B106" t="s">
-        <v>9</v>
-      </c>
-      <c r="D106">
-        <v>0.5</v>
-      </c>
-      <c r="G106">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B107" t="s">
-        <v>10</v>
-      </c>
-      <c r="C107" t="s">
-        <v>11</v>
-      </c>
-      <c r="D107">
-        <v>20</v>
-      </c>
-      <c r="G107">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B108" t="s">
-        <v>44</v>
-      </c>
-      <c r="C108" t="s">
-        <v>45</v>
-      </c>
-      <c r="D108">
-        <f>0.2*0.15</f>
-        <v>0.03</v>
-      </c>
-      <c r="G108">
-        <f>0.2*0.1</f>
-        <v>2.0000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B109" t="s">
-        <v>68</v>
-      </c>
-      <c r="C109" t="s">
-        <v>45</v>
-      </c>
-      <c r="D109">
-        <f>0.2*0.85</f>
-        <v>0.17</v>
-      </c>
-      <c r="G109">
-        <f>0.2*0.9</f>
-        <v>0.18000000000000002</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>95</v>
-      </c>
-      <c r="B110" t="s">
-        <v>6</v>
-      </c>
-      <c r="C110" t="s">
-        <v>23</v>
-      </c>
-      <c r="D110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B111" t="s">
-        <v>7</v>
-      </c>
-      <c r="C111" t="s">
-        <v>23</v>
-      </c>
-      <c r="D111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B112" t="s">
-        <v>8</v>
-      </c>
-      <c r="C112" t="s">
-        <v>22</v>
-      </c>
-      <c r="D112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B113" t="s">
-        <v>9</v>
-      </c>
-      <c r="C113" t="s">
-        <v>20</v>
-      </c>
-      <c r="D113">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B114" t="s">
-        <v>10</v>
-      </c>
-      <c r="C114" t="s">
-        <v>11</v>
-      </c>
-      <c r="D114">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
-        <v>97</v>
-      </c>
-      <c r="B115" t="s">
-        <v>6</v>
-      </c>
-      <c r="C115" t="s">
-        <v>23</v>
-      </c>
-      <c r="D115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B116" t="s">
-        <v>7</v>
-      </c>
-      <c r="C116" t="s">
-        <v>23</v>
-      </c>
-      <c r="D116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B117" t="s">
-        <v>8</v>
-      </c>
-      <c r="C117" t="s">
-        <v>22</v>
-      </c>
-      <c r="D117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B118" t="s">
-        <v>9</v>
-      </c>
-      <c r="C118" t="s">
-        <v>20</v>
-      </c>
-      <c r="D118">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B119" t="s">
-        <v>10</v>
-      </c>
-      <c r="C119" t="s">
-        <v>11</v>
-      </c>
-      <c r="D119">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B120" t="s">
-        <v>44</v>
-      </c>
-      <c r="C120" t="s">
-        <v>45</v>
-      </c>
-      <c r="D120">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
-        <v>94</v>
-      </c>
-      <c r="B121" t="s">
-        <v>6</v>
-      </c>
-      <c r="C121" t="s">
-        <v>21</v>
-      </c>
-      <c r="D121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B122" t="s">
-        <v>7</v>
-      </c>
-      <c r="C122" t="s">
-        <v>21</v>
-      </c>
-      <c r="D122">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B123" t="s">
-        <v>8</v>
-      </c>
-      <c r="C123" t="s">
-        <v>22</v>
-      </c>
-      <c r="D123">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B124" t="s">
-        <v>9</v>
-      </c>
-      <c r="D124">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B125" t="s">
-        <v>10</v>
-      </c>
-      <c r="C125" t="s">
-        <v>11</v>
-      </c>
-      <c r="D125">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B126" t="s">
-        <v>44</v>
-      </c>
-      <c r="C126" t="s">
-        <v>45</v>
-      </c>
-      <c r="D126">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A127" t="s">
-        <v>100</v>
-      </c>
-      <c r="B127" t="s">
-        <v>6</v>
-      </c>
-      <c r="C127" t="s">
-        <v>21</v>
-      </c>
-      <c r="D127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B128" t="s">
-        <v>7</v>
-      </c>
-      <c r="C128" t="s">
-        <v>21</v>
-      </c>
-      <c r="D128">
-        <f>D127*0.05</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B129" t="s">
-        <v>8</v>
-      </c>
-      <c r="C129" t="s">
-        <v>22</v>
-      </c>
-      <c r="D129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B130" t="s">
-        <v>9</v>
-      </c>
-      <c r="D130">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B131" t="s">
-        <v>10</v>
-      </c>
-      <c r="C131" t="s">
-        <v>11</v>
-      </c>
-      <c r="D131">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B132" t="s">
-        <v>44</v>
-      </c>
-      <c r="C132" t="s">
-        <v>45</v>
-      </c>
-      <c r="D132">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
-        <v>98</v>
-      </c>
-      <c r="B133" t="s">
-        <v>6</v>
-      </c>
-      <c r="C133" t="s">
-        <v>21</v>
-      </c>
-      <c r="D133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B134" t="s">
-        <v>7</v>
-      </c>
-      <c r="C134" t="s">
-        <v>21</v>
-      </c>
-      <c r="D134">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B135" t="s">
-        <v>8</v>
-      </c>
-      <c r="C135" t="s">
-        <v>22</v>
-      </c>
-      <c r="D135">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B136" t="s">
-        <v>9</v>
-      </c>
-      <c r="D136">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B137" t="s">
-        <v>10</v>
-      </c>
-      <c r="C137" t="s">
-        <v>11</v>
-      </c>
-      <c r="D137">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B138" t="s">
-        <v>44</v>
-      </c>
-      <c r="C138" t="s">
-        <v>45</v>
-      </c>
-      <c r="D138">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
-        <v>99</v>
-      </c>
-      <c r="B139" t="s">
-        <v>6</v>
-      </c>
-      <c r="C139" t="s">
-        <v>21</v>
-      </c>
-      <c r="D139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B140" t="s">
-        <v>7</v>
-      </c>
-      <c r="C140" t="s">
-        <v>21</v>
-      </c>
-      <c r="D140">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B141" t="s">
-        <v>8</v>
-      </c>
-      <c r="C141" t="s">
-        <v>22</v>
-      </c>
-      <c r="D141">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B142" t="s">
-        <v>9</v>
-      </c>
-      <c r="D142">
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B143" t="s">
-        <v>10</v>
-      </c>
-      <c r="C143" t="s">
-        <v>11</v>
-      </c>
-      <c r="D143">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B144" t="s">
-        <v>44</v>
-      </c>
-      <c r="C144" t="s">
-        <v>45</v>
-      </c>
-      <c r="D144">
-        <v>0.2</v>
-      </c>
+      <c r="E144" s="4"/>
+      <c r="F144" s="4"/>
+      <c r="G144" s="4"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
@@ -4982,7 +5344,7 @@
         <v>21</v>
       </c>
       <c r="D145">
-        <v>720</v>
+        <v>845</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
@@ -4994,7 +5356,7 @@
       </c>
       <c r="D146">
         <f>0.047*D145</f>
-        <v>33.840000000000003</v>
+        <v>39.715000000000003</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
@@ -5046,7 +5408,7 @@
         <v>21</v>
       </c>
       <c r="D151">
-        <v>1420</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
@@ -5057,8 +5419,8 @@
         <v>21</v>
       </c>
       <c r="D152">
-        <f>0.04*D151</f>
-        <v>56.800000000000004</v>
+        <f>0.035*D151</f>
+        <v>55.125000000000007</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
@@ -5125,11 +5487,11 @@
       <c r="C158" t="s">
         <v>21</v>
       </c>
-      <c r="D158" s="2">
-        <v>2263</v>
+      <c r="D158">
+        <v>1325</v>
       </c>
       <c r="G158">
-        <v>1257.3345999999999</v>
+        <v>395</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
@@ -5140,11 +5502,12 @@
         <v>21</v>
       </c>
       <c r="D159">
-        <f>0.04*D158</f>
-        <v>90.52</v>
+        <f>0.03*D158</f>
+        <v>39.75</v>
       </c>
       <c r="G159">
-        <v>50.29</v>
+        <f t="shared" ref="E159:G159" si="0">0.03*G158</f>
+        <v>11.85</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
@@ -5160,10 +5523,10 @@
         <v>9</v>
       </c>
       <c r="D161">
-        <v>0.57999999999999996</v>
+        <v>0.64</v>
       </c>
       <c r="G161">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
@@ -5199,7 +5562,7 @@
         <v>21</v>
       </c>
       <c r="D164">
-        <v>33.840000000000003</v>
+        <v>39.715000000000003</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.2">
@@ -5259,7 +5622,7 @@
         <v>21</v>
       </c>
       <c r="D170">
-        <v>56.8</v>
+        <v>55.125</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.2">
@@ -5326,7 +5689,7 @@
       <c r="C176" t="s">
         <v>21</v>
       </c>
-      <c r="D176" s="2"/>
+      <c r="D176" s="1"/>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B177" t="s">
@@ -5336,7 +5699,7 @@
         <v>21</v>
       </c>
       <c r="D177">
-        <v>90.52</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
@@ -5352,7 +5715,7 @@
         <v>9</v>
       </c>
       <c r="D179">
-        <v>0.57999999999999996</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.2">
@@ -5469,7 +5832,7 @@
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A190" s="3"/>
+      <c r="A190" s="2"/>
       <c r="B190" t="s">
         <v>9</v>
       </c>
@@ -5689,7 +6052,7 @@
       <c r="E11">
         <v>24771.661</v>
       </c>
-      <c r="G11" s="2"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -5721,7 +6084,7 @@
       <c r="E13">
         <v>6954.8180000000002</v>
       </c>
-      <c r="G13" s="2"/>
+      <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -5809,7 +6172,7 @@
       <c r="D19">
         <v>4</v>
       </c>
-      <c r="G19" s="2"/>
+      <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">

--- a/FinalModel/input_databases/default/technologies.xlsx
+++ b/FinalModel/input_databases/default/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nzuijder/Documents/MSc_CSP/MfT/Individual_model/Individual/FinalModel/input_databases/default/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A34584-CA1D-2640-BC49-D90659B4CF97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE7D714-7872-E44D-B0B3-F7894809070D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="static_parameters" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="117">
   <si>
     <t>Technology</t>
   </si>
@@ -387,6 +387,12 @@
   </si>
   <si>
     <t>Industrial LTP</t>
+  </si>
+  <si>
+    <t>Industrial gas boiler - existing</t>
+  </si>
+  <si>
+    <t>Large-scale heat pump - existing</t>
   </si>
 </sst>
 </file>
@@ -726,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2AEF3F7-9EA9-4235-9872-78FDC34EDD32}">
-  <dimension ref="A1:F197"/>
+  <dimension ref="A1:F209"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.83203125" bestFit="1" customWidth="1"/>
@@ -2821,7 +2827,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B193" t="s">
         <v>16</v>
       </c>
@@ -2829,7 +2835,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B194" t="s">
         <v>24</v>
       </c>
@@ -2837,7 +2843,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B195" t="s">
         <v>28</v>
       </c>
@@ -2848,7 +2854,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B196" t="s">
         <v>31</v>
       </c>
@@ -2862,7 +2868,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="197" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B197" t="s">
         <v>46</v>
       </c>
@@ -2873,6 +2879,138 @@
         <v>44</v>
       </c>
       <c r="E197" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>115</v>
+      </c>
+      <c r="B198" t="s">
+        <v>49</v>
+      </c>
+      <c r="E198" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="E199" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B200" t="s">
+        <v>24</v>
+      </c>
+      <c r="E200" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B201" t="s">
+        <v>28</v>
+      </c>
+      <c r="C201" t="s">
+        <v>29</v>
+      </c>
+      <c r="E201" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B202" t="s">
+        <v>31</v>
+      </c>
+      <c r="C202" t="s">
+        <v>32</v>
+      </c>
+      <c r="D202" t="s">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B203" t="s">
+        <v>46</v>
+      </c>
+      <c r="C203" t="s">
+        <v>47</v>
+      </c>
+      <c r="D203" t="s">
+        <v>44</v>
+      </c>
+      <c r="E203" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>116</v>
+      </c>
+      <c r="B204" t="s">
+        <v>49</v>
+      </c>
+      <c r="E204" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B205" t="s">
+        <v>16</v>
+      </c>
+      <c r="E205" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B206" t="s">
+        <v>24</v>
+      </c>
+      <c r="E206" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B207" t="s">
+        <v>28</v>
+      </c>
+      <c r="C207" t="s">
+        <v>29</v>
+      </c>
+      <c r="E207" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B208" t="s">
+        <v>31</v>
+      </c>
+      <c r="C208" t="s">
+        <v>32</v>
+      </c>
+      <c r="D208" t="s">
+        <v>9</v>
+      </c>
+      <c r="E208" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="209" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B209" t="s">
+        <v>46</v>
+      </c>
+      <c r="C209" t="s">
+        <v>47</v>
+      </c>
+      <c r="D209" t="s">
+        <v>44</v>
+      </c>
+      <c r="E209" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2885,7 +3023,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G204"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.83203125" bestFit="1" customWidth="1"/>
@@ -5506,7 +5644,7 @@
         <v>39.75</v>
       </c>
       <c r="G159">
-        <f t="shared" ref="E159:G159" si="0">0.03*G158</f>
+        <f t="shared" ref="G159" si="0">0.03*G158</f>
         <v>11.85</v>
       </c>
     </row>
@@ -5859,6 +5997,127 @@
         <v>45</v>
       </c>
       <c r="D192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>115</v>
+      </c>
+      <c r="B193" t="s">
+        <v>6</v>
+      </c>
+      <c r="C193" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B194" t="s">
+        <v>7</v>
+      </c>
+      <c r="C194" t="s">
+        <v>21</v>
+      </c>
+      <c r="D194">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B195" t="s">
+        <v>8</v>
+      </c>
+      <c r="C195" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B196" t="s">
+        <v>9</v>
+      </c>
+      <c r="D196">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B197" t="s">
+        <v>10</v>
+      </c>
+      <c r="C197" t="s">
+        <v>11</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B198" t="s">
+        <v>44</v>
+      </c>
+      <c r="C198" t="s">
+        <v>45</v>
+      </c>
+      <c r="D198">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>116</v>
+      </c>
+      <c r="B199" t="s">
+        <v>6</v>
+      </c>
+      <c r="C199" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B200" t="s">
+        <v>7</v>
+      </c>
+      <c r="C200" t="s">
+        <v>21</v>
+      </c>
+      <c r="D200">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B201" t="s">
+        <v>8</v>
+      </c>
+      <c r="C201" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A202" s="2"/>
+      <c r="B202" t="s">
+        <v>9</v>
+      </c>
+      <c r="D202">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B203" t="s">
+        <v>10</v>
+      </c>
+      <c r="C203" t="s">
+        <v>11</v>
+      </c>
+      <c r="D203">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B204" t="s">
+        <v>44</v>
+      </c>
+      <c r="C204" t="s">
+        <v>45</v>
+      </c>
+      <c r="D204">
         <v>0</v>
       </c>
     </row>
@@ -5870,7 +6129,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD4172D-F773-442E-8F80-CF8D21EAB2CE}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.83203125" bestFit="1" customWidth="1"/>
@@ -6409,6 +6668,68 @@
         <v>0.7</v>
       </c>
     </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38">
+        <v>0.7</v>
+      </c>
+      <c r="E38">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39">
+        <v>0.7</v>
+      </c>
+      <c r="E39">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" t="s">
+        <v>92</v>
+      </c>
+      <c r="D40">
+        <v>0.7</v>
+      </c>
+      <c r="E40">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41">
+        <v>0.7</v>
+      </c>
+      <c r="E41">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/FinalModel/input_databases/default/technologies.xlsx
+++ b/FinalModel/input_databases/default/technologies.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE7D714-7872-E44D-B0B3-F7894809070D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="static_parameters" sheetId="2" r:id="rId1"/>

--- a/FinalModel/input_databases/default/technologies.xlsx
+++ b/FinalModel/input_databases/default/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nzuijder/Documents/MSc_CSP/MfT/Individual_model/Individual/FinalModel/input_databases/default/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE7D714-7872-E44D-B0B3-F7894809070D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A964C33B-69DD-CF48-BAE4-780E8EC0D682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="static_parameters" sheetId="2" r:id="rId1"/>
@@ -5504,6 +5504,9 @@
       <c r="C147" t="s">
         <v>22</v>
       </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B148" t="s">
@@ -5655,6 +5658,9 @@
       <c r="C160" t="s">
         <v>22</v>
       </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B161" t="s">
@@ -5751,6 +5757,9 @@
       <c r="C169" t="s">
         <v>21</v>
       </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B170" t="s">
@@ -5827,7 +5836,9 @@
       <c r="C176" t="s">
         <v>21</v>
       </c>
-      <c r="D176" s="1"/>
+      <c r="D176" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B177" t="s">
@@ -5847,6 +5858,9 @@
       <c r="C178" t="s">
         <v>22</v>
       </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B179" t="s">
@@ -6010,6 +6024,9 @@
       <c r="C193" t="s">
         <v>21</v>
       </c>
+      <c r="D193">
+        <v>0</v>
+      </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B194" t="s">
@@ -6029,6 +6046,9 @@
       <c r="C195" t="s">
         <v>22</v>
       </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B196" t="s">
@@ -6070,6 +6090,9 @@
       <c r="C199" t="s">
         <v>21</v>
       </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B200" t="s">
@@ -6088,6 +6111,9 @@
       </c>
       <c r="C201" t="s">
         <v>22</v>
+      </c>
+      <c r="D201">
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.2">
@@ -6137,6 +6163,8 @@
     <col min="3" max="3" width="7.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="8" width="8.1640625" customWidth="1"/>
+    <col min="9" max="9" width="24.6640625" customWidth="1"/>
+    <col min="11" max="11" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -6153,7 +6181,7 @@
         <v>90</v>
       </c>
       <c r="E1">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="F1">
         <v>2030</v>
@@ -6198,8 +6226,7 @@
         <v>0.7</v>
       </c>
       <c r="E4">
-        <f>17774.482-E6</f>
-        <v>15822.165999999999</v>
+        <v>11562.6</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -6213,8 +6240,7 @@
         <v>0.7</v>
       </c>
       <c r="E5">
-        <f>17774.482-E7</f>
-        <v>15822.165999999999</v>
+        <v>11562.6</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -6231,8 +6257,7 @@
         <v>0.7</v>
       </c>
       <c r="E6">
-        <f>975.445+188.771+788.1</f>
-        <v>1952.3160000000003</v>
+        <v>876.4</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -6246,8 +6271,7 @@
         <v>0.7</v>
       </c>
       <c r="E7">
-        <f>975.445+188.771+788.1</f>
-        <v>1952.3160000000003</v>
+        <v>876.4</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -6264,7 +6288,7 @@
         <v>0.7</v>
       </c>
       <c r="E8">
-        <v>512</v>
+        <v>358.4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -6278,7 +6302,7 @@
         <v>0.7</v>
       </c>
       <c r="E9">
-        <v>512</v>
+        <v>358.4</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -6295,7 +6319,7 @@
         <v>0.7</v>
       </c>
       <c r="E10">
-        <v>24771.661</v>
+        <v>7777</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -6309,9 +6333,8 @@
         <v>0.7</v>
       </c>
       <c r="E11">
-        <v>24771.661</v>
-      </c>
-      <c r="G11" s="1"/>
+        <v>7777</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -6327,7 +6350,7 @@
         <v>0.7</v>
       </c>
       <c r="E12">
-        <v>6954.8180000000002</v>
+        <v>2931.6</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -6341,9 +6364,8 @@
         <v>0.7</v>
       </c>
       <c r="E13">
-        <v>6954.8180000000002</v>
-      </c>
-      <c r="G13" s="1"/>
+        <v>2931.6</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -6359,7 +6381,7 @@
         <v>0.7</v>
       </c>
       <c r="E14">
-        <v>4747.5</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -6373,7 +6395,7 @@
         <v>0.7</v>
       </c>
       <c r="E15">
-        <v>4747.5</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -6390,10 +6412,10 @@
         <v>4</v>
       </c>
       <c r="E16">
-        <v>0.56914399999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>93</v>
       </c>
@@ -6404,10 +6426,10 @@
         <v>4</v>
       </c>
       <c r="E17">
-        <v>1.5691440000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -6421,7 +6443,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>93</v>
       </c>
@@ -6431,9 +6453,8 @@
       <c r="D19">
         <v>4</v>
       </c>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>97</v>
       </c>
@@ -6447,11 +6468,10 @@
         <v>4</v>
       </c>
       <c r="E20">
-        <f>9.24781-E17</f>
-        <v>7.6786659999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>93</v>
       </c>
@@ -6462,11 +6482,10 @@
         <v>4</v>
       </c>
       <c r="E21">
-        <f>9.24781-E17</f>
-        <v>7.6786659999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>98</v>
       </c>
@@ -6477,7 +6496,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>93</v>
       </c>
@@ -6485,7 +6504,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>99</v>
       </c>
@@ -6496,7 +6515,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>93</v>
       </c>
@@ -6504,7 +6523,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -6515,7 +6534,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>93</v>
       </c>
@@ -6523,7 +6542,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>110</v>
       </c>
@@ -6541,7 +6560,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>93</v>
       </c>
@@ -6556,7 +6575,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>111</v>
       </c>
@@ -6573,7 +6592,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>93</v>
       </c>
@@ -6587,7 +6606,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>109</v>
       </c>

--- a/FinalModel/input_databases/default/technologies.xlsx
+++ b/FinalModel/input_databases/default/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nzuijder/Documents/MSc_CSP/MfT/Individual_model/Individual/FinalModel/input_databases/default/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A964C33B-69DD-CF48-BAE4-780E8EC0D682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D0BD5B-63F3-7845-B6E6-E293B5D5B22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="static_parameters" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="117">
   <si>
     <t>Technology</t>
   </si>
@@ -732,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2AEF3F7-9EA9-4235-9872-78FDC34EDD32}">
-  <dimension ref="A1:F209"/>
+  <dimension ref="A1:F207"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.83203125" bestFit="1" customWidth="1"/>
@@ -2785,7 +2785,7 @@
         <v>29</v>
       </c>
       <c r="E189" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
@@ -2869,149 +2869,121 @@
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>115</v>
+      </c>
       <c r="B197" t="s">
-        <v>46</v>
-      </c>
-      <c r="C197" t="s">
-        <v>47</v>
-      </c>
-      <c r="D197" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E197" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A198" t="s">
-        <v>115</v>
-      </c>
       <c r="B198" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="E198" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B199" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E199" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B200" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="C200" t="s">
+        <v>29</v>
       </c>
       <c r="E200" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B201" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C201" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="D201" t="s">
+        <v>9</v>
       </c>
       <c r="E201" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B202" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C202" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D202" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="E202" t="s">
-        <v>114</v>
+        <v>48</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>116</v>
+      </c>
       <c r="B203" t="s">
-        <v>46</v>
-      </c>
-      <c r="C203" t="s">
-        <v>47</v>
-      </c>
-      <c r="D203" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E203" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A204" t="s">
-        <v>116</v>
-      </c>
       <c r="B204" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="E204" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B205" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E205" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B206" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="C206" t="s">
+        <v>29</v>
       </c>
       <c r="E206" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B207" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C207" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="D207" t="s">
+        <v>9</v>
       </c>
       <c r="E207" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B208" t="s">
-        <v>31</v>
-      </c>
-      <c r="C208" t="s">
-        <v>32</v>
-      </c>
-      <c r="D208" t="s">
-        <v>9</v>
-      </c>
-      <c r="E208" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="209" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B209" t="s">
-        <v>46</v>
-      </c>
-      <c r="C209" t="s">
-        <v>47</v>
-      </c>
-      <c r="D209" t="s">
-        <v>44</v>
-      </c>
-      <c r="E209" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/FinalModel/input_databases/default/technologies.xlsx
+++ b/FinalModel/input_databases/default/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nzuijder/Documents/MSc_CSP/MfT/Individual_model/Individual/FinalModel/input_databases/default/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D0BD5B-63F3-7845-B6E6-E293B5D5B22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1E88E1-C812-8A4F-805F-DE7F1FCFF5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="static_parameters" sheetId="2" r:id="rId1"/>
@@ -2995,7 +2995,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G204"/>
+  <dimension ref="A1:Q204"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.83203125" bestFit="1" customWidth="1"/>
@@ -3911,7 +3911,7 @@
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>40</v>
       </c>
@@ -3928,7 +3928,7 @@
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
       <c r="B50" s="3" t="s">
         <v>7</v>
@@ -3943,7 +3943,7 @@
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
       <c r="B51" s="3" t="s">
         <v>8</v>
@@ -3958,7 +3958,7 @@
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
       <c r="B52" s="3" t="s">
         <v>9</v>
@@ -3973,7 +3973,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
       <c r="B53" s="3" t="s">
         <v>10</v>
@@ -3988,7 +3988,7 @@
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>64</v>
       </c>
@@ -4005,7 +4005,7 @@
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
       <c r="B55" s="3" t="s">
         <v>7</v>
@@ -4020,7 +4020,7 @@
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
       <c r="B56" s="3" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
       <c r="B57" s="3" t="s">
         <v>9</v>
@@ -4048,7 +4048,7 @@
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="B58" s="3" t="s">
         <v>10</v>
@@ -4063,7 +4063,7 @@
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
       <c r="B59" s="3" t="s">
         <v>44</v>
@@ -4079,8 +4079,12 @@
       <c r="G59" s="3">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
       <c r="B60" s="3" t="s">
         <v>68</v>
@@ -4096,8 +4100,15 @@
       <c r="G60" s="3">
         <v>0.19</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>70</v>
       </c>
@@ -4113,8 +4124,15 @@
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="K61" s="4"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
       <c r="B62" s="3" t="s">
         <v>7</v>
@@ -4128,8 +4146,15 @@
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="K62" s="4"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
       <c r="B63" s="3" t="s">
         <v>8</v>
@@ -4143,8 +4168,15 @@
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="K63" s="4"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
       <c r="B64" s="3" t="s">
         <v>9</v>
@@ -4156,8 +4188,15 @@
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="K64" s="4"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
       <c r="B65" s="3" t="s">
         <v>10</v>
@@ -4171,8 +4210,15 @@
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="K65" s="4"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
       <c r="B66" s="3" t="s">
         <v>44</v>
@@ -4186,10 +4232,10 @@
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
       <c r="G66" s="3">
-        <v>-396</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+        <v>-0.39600000000000002</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
       <c r="B67" s="3" t="s">
         <v>68</v>
@@ -4203,10 +4249,10 @@
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
       <c r="G67" s="3">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0.39600000000000002</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>72</v>
       </c>
@@ -4225,7 +4271,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="B69" s="3" t="s">
         <v>7</v>
@@ -4240,7 +4286,7 @@
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
       <c r="B70" s="3" t="s">
         <v>8</v>
@@ -4255,7 +4301,7 @@
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
       <c r="B71" s="3" t="s">
         <v>9</v>
@@ -4270,7 +4316,7 @@
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
       <c r="B72" s="3" t="s">
         <v>10</v>
@@ -4285,7 +4331,7 @@
       <c r="F72" s="4"/>
       <c r="G72" s="4"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
       <c r="B73" s="3" t="s">
         <v>44</v>
@@ -4300,7 +4346,7 @@
       <c r="F73" s="4"/>
       <c r="G73" s="4"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>75</v>
       </c>
@@ -4321,7 +4367,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
       <c r="B75" s="3" t="s">
         <v>7</v>
@@ -4340,7 +4386,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
       <c r="B76" s="3" t="s">
         <v>8</v>
@@ -4355,7 +4401,7 @@
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
       <c r="B77" s="3" t="s">
         <v>9</v>
@@ -4372,7 +4418,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
       <c r="B78" s="3" t="s">
         <v>10</v>
@@ -4387,7 +4433,7 @@
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>77</v>
       </c>
@@ -4406,7 +4452,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
       <c r="B80" s="3" t="s">
         <v>7</v>

--- a/FinalModel/input_databases/default/technologies.xlsx
+++ b/FinalModel/input_databases/default/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nzuijder/Documents/MSc_CSP/MfT/Individual_model/Individual/FinalModel/input_databases/default/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1E88E1-C812-8A4F-805F-DE7F1FCFF5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E3CF0F-E899-4440-BC5F-3043E7BCAD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="static_parameters" sheetId="2" r:id="rId1"/>
